--- a/skills/builtin/xlsx/fixtures/narrow.xlsx
+++ b/skills/builtin/xlsx/fixtures/narrow.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
@@ -58,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -608,13 +613,13 @@
           <t>营业收入</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>1240</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>1103</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <f>B3/C3-1</f>
         <v/>
       </c>
@@ -625,13 +630,13 @@
           <t>营业成本</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>769</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="3" t="n">
         <v>702</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <f>B4/C4-1</f>
         <v/>
       </c>
@@ -650,7 +655,7 @@
         <f>C3-C4</f>
         <v/>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <f>B5/C5-1</f>
         <v/>
       </c>
@@ -719,7 +724,7 @@
           <t>毛利率</t>
         </is>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <f>B2/利润表!B3</f>
         <v/>
       </c>
